--- a/花境设计素材库/数据库26.10.10（初版100种更新+新品种58）.xlsx
+++ b/花境设计素材库/数据库26.10.10（初版100种更新+新品种58）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\work\工作室——设计文件（研究学习的重要资料）\01个人文件\Twolobster 2026\花境设计素材库\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239FE125-7967-459D-9541-F37CDC483C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE8EBFF-554B-46D6-A2B6-7E31930328AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="678">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2410,6 +2410,174 @@
   </si>
   <si>
     <t>20—30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牡丹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉花绣线菊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>矾根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北葱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贯叶金丝桃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剪秋萝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无尽夏绣球花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皱叶剪秋萝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金叶莸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千禧葱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瞿麦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早开堇菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋覆花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地黄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*蛇莓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱茎苦麦菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金莲花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藿香蓟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石竹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香雪球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄花鸢尾（黄菖蒲）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄芩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丹参</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美丽飞蓬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄花菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山丹百合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银灰鼠尾草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红脉酸模</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>细茎针茅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铃兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钓钟柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三七景天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白毛马鞭草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芦竹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大油芒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长序芒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土木香</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙舌兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美洲龙舌兰</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2461,7 +2629,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2528,6 +2696,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2580,7 +2754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2619,6 +2793,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3525,11 +3700,11 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="34" t="s">
         <v>604</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>523</v>
+        <v>669</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>31</v>
@@ -3556,11 +3731,11 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="34" t="s">
         <v>605</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>58</v>
+        <v>670</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>31</v>
@@ -3587,11 +3762,11 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="34" t="s">
         <v>606</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>39</v>
+        <v>671</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>31</v>
@@ -3618,11 +3793,11 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="34" t="s">
         <v>607</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>46</v>
+        <v>672</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>30</v>
@@ -3649,11 +3824,11 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="34" t="s">
         <v>608</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>57</v>
+        <v>673</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -3680,11 +3855,11 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="34" t="s">
         <v>609</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>59</v>
+        <v>674</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
@@ -3711,11 +3886,11 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="34" t="s">
         <v>610</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>61</v>
+        <v>675</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
@@ -3742,7 +3917,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="34" t="s">
         <v>611</v>
       </c>
       <c r="C28" s="33" t="s">
@@ -3773,11 +3948,11 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="34" t="s">
         <v>612</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>544</v>
+        <v>676</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
@@ -3804,11 +3979,11 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="34" t="s">
         <v>613</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>545</v>
+        <v>677</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -4191,7 +4366,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="34" t="s">
         <v>555</v>
       </c>
       <c r="C43" s="33" t="s">
@@ -4222,7 +4397,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="34" t="s">
         <v>562</v>
       </c>
       <c r="C44" s="33" t="s">
@@ -4253,11 +4428,11 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
-      <c r="B45" s="33" t="s">
+      <c r="B45" s="34" t="s">
         <v>563</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>529</v>
+        <v>636</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>31</v>
@@ -4284,11 +4459,11 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
-      <c r="B46" s="33" t="s">
+      <c r="B46" s="34" t="s">
         <v>561</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>527</v>
+        <v>637</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>31</v>
@@ -4315,11 +4490,11 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
-      <c r="B47" s="33" t="s">
+      <c r="B47" s="34" t="s">
         <v>564</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>532</v>
+        <v>638</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>354</v>
@@ -4346,11 +4521,11 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="34" t="s">
         <v>565</v>
       </c>
       <c r="C48" s="33" t="s">
-        <v>533</v>
+        <v>639</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
@@ -4377,11 +4552,11 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
-      <c r="B49" s="33" t="s">
+      <c r="B49" s="34" t="s">
         <v>566</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>539</v>
+        <v>640</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>31</v>
@@ -4408,11 +4583,11 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
-      <c r="B50" s="33" t="s">
+      <c r="B50" s="34" t="s">
         <v>567</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>543</v>
+        <v>641</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>31</v>
@@ -4439,7 +4614,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
-      <c r="B51" s="33" t="s">
+      <c r="B51" s="34" t="s">
         <v>568</v>
       </c>
       <c r="C51" s="33" t="s">
@@ -4470,11 +4645,11 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
-      <c r="B52" s="33" t="s">
+      <c r="B52" s="34" t="s">
         <v>569</v>
       </c>
       <c r="C52" s="33" t="s">
-        <v>546</v>
+        <v>642</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>85</v>
@@ -4501,11 +4676,11 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
-      <c r="B53" s="33" t="s">
+      <c r="B53" s="34" t="s">
         <v>556</v>
       </c>
       <c r="C53" s="33" t="s">
-        <v>49</v>
+        <v>643</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
@@ -4594,11 +4769,11 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="34" t="s">
         <v>559</v>
       </c>
       <c r="C56" s="33" t="s">
-        <v>62</v>
+        <v>644</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>30</v>
@@ -4625,11 +4800,11 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
-      <c r="B57" s="33" t="s">
+      <c r="B57" s="34" t="s">
         <v>560</v>
       </c>
       <c r="C57" s="33" t="s">
-        <v>526</v>
+        <v>645</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>30</v>
@@ -6004,11 +6179,11 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
-      <c r="B102" s="33" t="s">
+      <c r="B102" s="34" t="s">
         <v>582</v>
       </c>
       <c r="C102" s="33" t="s">
-        <v>48</v>
+        <v>656</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>175</v>
@@ -6035,11 +6210,11 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
-      <c r="B103" s="33" t="s">
+      <c r="B103" s="34" t="s">
         <v>583</v>
       </c>
       <c r="C103" s="33" t="s">
-        <v>40</v>
+        <v>657</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>30</v>
@@ -6066,11 +6241,11 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
-      <c r="B104" s="33" t="s">
+      <c r="B104" s="34" t="s">
         <v>584</v>
       </c>
       <c r="C104" s="33" t="s">
-        <v>42</v>
+        <v>658</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>31</v>
@@ -6128,11 +6303,11 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
-      <c r="B106" s="33" t="s">
+      <c r="B106" s="34" t="s">
         <v>586</v>
       </c>
       <c r="C106" s="33" t="s">
-        <v>38</v>
+        <v>659</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>30</v>
@@ -6159,11 +6334,11 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
-      <c r="B107" s="33" t="s">
+      <c r="B107" s="34" t="s">
         <v>587</v>
       </c>
       <c r="C107" s="33" t="s">
-        <v>60</v>
+        <v>660</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>31</v>
@@ -6190,7 +6365,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
-      <c r="B108" s="33" t="s">
+      <c r="B108" s="34" t="s">
         <v>588</v>
       </c>
       <c r="C108" s="33" t="s">
@@ -6221,7 +6396,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
-      <c r="B109" s="33" t="s">
+      <c r="B109" s="34" t="s">
         <v>589</v>
       </c>
       <c r="C109" s="33" t="s">
@@ -6252,11 +6427,11 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
-      <c r="B110" s="33" t="s">
+      <c r="B110" s="34" t="s">
         <v>590</v>
       </c>
       <c r="C110" s="33" t="s">
-        <v>530</v>
+        <v>661</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>31</v>
@@ -6314,11 +6489,11 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
-      <c r="B112" s="33" t="s">
+      <c r="B112" s="34" t="s">
         <v>592</v>
       </c>
       <c r="C112" s="33" t="s">
-        <v>536</v>
+        <v>662</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>30</v>
@@ -6345,11 +6520,11 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
-      <c r="B113" s="33" t="s">
+      <c r="B113" s="34" t="s">
         <v>593</v>
       </c>
       <c r="C113" s="33" t="s">
-        <v>538</v>
+        <v>663</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>31</v>
@@ -6376,11 +6551,11 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
-      <c r="B114" s="33" t="s">
+      <c r="B114" s="34" t="s">
         <v>594</v>
       </c>
       <c r="C114" s="33" t="s">
-        <v>542</v>
+        <v>664</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>31</v>
@@ -7042,11 +7217,11 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
-      <c r="B136" s="33" t="s">
+      <c r="B136" s="34" t="s">
         <v>596</v>
       </c>
       <c r="C136" s="33" t="s">
-        <v>522</v>
+        <v>665</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>31</v>
@@ -7135,11 +7310,11 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
-      <c r="B139" s="33" t="s">
+      <c r="B139" s="34" t="s">
         <v>599</v>
       </c>
       <c r="C139" s="33" t="s">
-        <v>52</v>
+        <v>666</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>149</v>
@@ -7166,7 +7341,7 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
-      <c r="B140" s="33" t="s">
+      <c r="B140" s="34" t="s">
         <v>600</v>
       </c>
       <c r="C140" s="33" t="s">
@@ -7197,11 +7372,11 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
-      <c r="B141" s="33" t="s">
+      <c r="B141" s="34" t="s">
         <v>601</v>
       </c>
       <c r="C141" s="33" t="s">
-        <v>534</v>
+        <v>667</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>30</v>
@@ -7228,11 +7403,11 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
-      <c r="B142" s="33" t="s">
+      <c r="B142" s="34" t="s">
         <v>602</v>
       </c>
       <c r="C142" s="33" t="s">
-        <v>535</v>
+        <v>668</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>30</v>
@@ -7259,7 +7434,7 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
-      <c r="B143" s="33" t="s">
+      <c r="B143" s="34" t="s">
         <v>603</v>
       </c>
       <c r="C143" s="33" t="s">
@@ -7553,11 +7728,11 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
-      <c r="B153" s="33" t="s">
+      <c r="B153" s="34" t="s">
         <v>570</v>
       </c>
       <c r="C153" s="33" t="s">
-        <v>47</v>
+        <v>646</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>30</v>
@@ -7584,11 +7759,11 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
-      <c r="B154" s="33" t="s">
+      <c r="B154" s="34" t="s">
         <v>571</v>
       </c>
       <c r="C154" s="33" t="s">
-        <v>54</v>
+        <v>647</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>354</v>
@@ -7615,11 +7790,11 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
-      <c r="B155" s="33" t="s">
+      <c r="B155" s="34" t="s">
         <v>572</v>
       </c>
       <c r="C155" s="33" t="s">
-        <v>55</v>
+        <v>648</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>31</v>
@@ -7646,11 +7821,11 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
-      <c r="B156" s="33" t="s">
+      <c r="B156" s="34" t="s">
         <v>573</v>
       </c>
       <c r="C156" s="33" t="s">
-        <v>56</v>
+        <v>649</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>30</v>
@@ -7677,11 +7852,11 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
-      <c r="B157" s="33" t="s">
+      <c r="B157" s="34" t="s">
         <v>574</v>
       </c>
       <c r="C157" s="33" t="s">
-        <v>524</v>
+        <v>650</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>354</v>
@@ -7708,11 +7883,11 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
-      <c r="B158" s="33" t="s">
+      <c r="B158" s="34" t="s">
         <v>575</v>
       </c>
       <c r="C158" s="33" t="s">
-        <v>53</v>
+        <v>651</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>354</v>
@@ -7739,11 +7914,11 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
-      <c r="B159" s="33" t="s">
+      <c r="B159" s="34" t="s">
         <v>576</v>
       </c>
       <c r="C159" s="33" t="s">
-        <v>51</v>
+        <v>652</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>31</v>
@@ -7770,7 +7945,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
-      <c r="B160" s="33" t="s">
+      <c r="B160" s="34" t="s">
         <v>577</v>
       </c>
       <c r="C160" s="33" t="s">
@@ -7832,11 +8007,11 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
-      <c r="B162" s="33" t="s">
+      <c r="B162" s="34" t="s">
         <v>579</v>
       </c>
       <c r="C162" s="33" t="s">
-        <v>537</v>
+        <v>653</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>30</v>
@@ -7863,11 +8038,11 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
-      <c r="B163" s="33" t="s">
+      <c r="B163" s="34" t="s">
         <v>580</v>
       </c>
       <c r="C163" s="33" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>31</v>
@@ -7894,11 +8069,11 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
-      <c r="B164" s="33" t="s">
+      <c r="B164" s="34" t="s">
         <v>581</v>
       </c>
       <c r="C164" s="33" t="s">
-        <v>541</v>
+        <v>655</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>30</v>
